--- a/data/trans_camb/P1421-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1421-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,93</t>
+          <t>-1,11; 1,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,17</t>
+          <t>-1,65; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,23</t>
+          <t>-0,42; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,79</t>
+          <t>-2,09; 2,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,75</t>
+          <t>-3,11; 1,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 12,33</t>
+          <t>2,82; 12,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,65</t>
+          <t>-1,05; 1,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,65</t>
+          <t>-1,8; 0,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,26</t>
+          <t>1,87; 7,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192,65%</t>
+          <t>186,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210,6%</t>
+          <t>211,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>190,8%</t>
+          <t>200,44%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 434,58</t>
+          <t>-70,41; 404,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 314,95</t>
+          <t>-100,0; 239,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 1030,95</t>
+          <t>-70,53; 1100,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 120,14</t>
+          <t>-51,69; 127,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,11; 40,98</t>
+          <t>-71,91; 68,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,8; 513,38</t>
+          <t>60,52; 538,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,92; 107,36</t>
+          <t>-42,83; 108,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 45,92</t>
+          <t>-65,67; 54,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,05; 432,23</t>
+          <t>62,09; 438,27</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,18</t>
+          <t>-2,32; 0,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,08</t>
+          <t>-2,6; -0,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,98</t>
+          <t>0,25; 5,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -1,55</t>
+          <t>-6,72; -1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,99</t>
+          <t>-3,82; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,04</t>
+          <t>-0,78; 6,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,88</t>
+          <t>-3,85; -1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,55</t>
+          <t>-2,63; 0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,26</t>
+          <t>0,69; 5,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130,52%</t>
+          <t>122,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,81; 21,67</t>
+          <t>-79,42; 31,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,86; 8,6</t>
+          <t>-92,18; 5,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 383,12</t>
+          <t>3,67; 368,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -22,87</t>
+          <t>-73,52; -22,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 34,15</t>
+          <t>-41,7; 33,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 95,43</t>
+          <t>-11,18; 109,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,88; -22,02</t>
+          <t>-68,22; -23,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 15,87</t>
+          <t>-46,62; 18,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 133,79</t>
+          <t>11,41; 133,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,98</t>
+          <t>-1,94; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,43</t>
+          <t>-2,47; 0,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,08</t>
+          <t>0,8; 5,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,65</t>
+          <t>-1,65; 3,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -0,88</t>
+          <t>-5,29; -0,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,24</t>
+          <t>1,79; 7,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,8</t>
+          <t>-1,35; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,65</t>
+          <t>-3,54; -0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,7</t>
+          <t>1,78; 5,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165,11%</t>
+          <t>132,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 78,34</t>
+          <t>-66,75; 88,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,03; 51,77</t>
+          <t>-81,9; 41,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,96; 413,99</t>
+          <t>23,02; 398,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 74,69</t>
+          <t>-23,1; 78,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,53; -13,63</t>
+          <t>-71,27; -9,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,6; 159,14</t>
+          <t>23,81; 155,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 54,01</t>
+          <t>-27,37; 57,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,55; -16,9</t>
+          <t>-68,92; -19,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,97; 160,8</t>
+          <t>34,5; 158,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,57</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,3</t>
+          <t>-3,67; -0,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,55</t>
+          <t>-2,93; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,87</t>
+          <t>1,18; 5,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,6</t>
+          <t>-3,1; 2,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,15</t>
+          <t>-3,25; 2,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,72</t>
+          <t>5,64; 11,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,49</t>
+          <t>-2,92; 0,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,85</t>
+          <t>-2,45; 0,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,36</t>
+          <t>4,03; 7,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>121,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>141,23%</t>
+          <t>140,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104,89%</t>
+          <t>137,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,22; -0,97</t>
+          <t>-89,97; -3,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 48,67</t>
+          <t>-71,8; 44,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 254,5</t>
+          <t>23,91; 341,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 57,23</t>
+          <t>-43,24; 58,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 48,06</t>
+          <t>-45,43; 45,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,71; 258,63</t>
+          <t>68,86; 256,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 13,29</t>
+          <t>-53,03; 14,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 26,83</t>
+          <t>-46,69; 22,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,38; 195,64</t>
+          <t>71,29; 221,38</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,57</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -0,96</t>
+          <t>-6,05; -1,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,24</t>
+          <t>-5,17; 0,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,36</t>
+          <t>-2,93; 2,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,57</t>
+          <t>-3,72; 2,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,93</t>
+          <t>-2,08; 4,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,39</t>
+          <t>3,66; 9,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,47</t>
+          <t>-3,97; -0,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,85</t>
+          <t>-2,16; 1,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,2</t>
+          <t>1,1; 5,17</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,01%</t>
+          <t>-3,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>118,83%</t>
+          <t>122,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-94,81; -29,01</t>
+          <t>-94,71; -30,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,94; 27,34</t>
+          <t>-80,3; 22,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 89,95</t>
+          <t>-46,87; 91,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 65,17</t>
+          <t>-51,04; 60,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 120,65</t>
+          <t>-29,95; 121,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,38; 245,73</t>
+          <t>47,88; 263,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 13,7</t>
+          <t>-64,01; -4,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 50,39</t>
+          <t>-37,31; 56,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18,82; 135,58</t>
+          <t>17,59; 142,67</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,42</t>
+          <t>-3,58; 0,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,58</t>
+          <t>-3,43; 0,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,56</t>
+          <t>-1,44; 3,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,31</t>
+          <t>-4,48; 2,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,0</t>
+          <t>-4,57; 2,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,89</t>
+          <t>-1,66; 5,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,01</t>
+          <t>-3,69; 0,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,24</t>
+          <t>-3,27; 1,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,17</t>
+          <t>-0,71; 3,2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-20,36%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,0%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-91,16; 83,22</t>
+          <t>-100,0; 75,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,76; 67,66</t>
+          <t>-90,62; 99,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 285,88</t>
+          <t>-41,8; 237,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 61,67</t>
+          <t>-49,72; 53,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,91; 57,71</t>
+          <t>-48,68; 43,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 47,83</t>
+          <t>-18,49; 100,2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 26,07</t>
+          <t>-56,99; 22,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 30,62</t>
+          <t>-52,65; 29,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 52,12</t>
+          <t>-11,38; 84,78</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,14</t>
+          <t>-4,66; 0,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,48</t>
+          <t>-2,93; 2,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,83</t>
+          <t>-1,74; 4,11</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,94</t>
+          <t>-0,5; 6,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,91</t>
+          <t>1,43; 9,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,56</t>
+          <t>3,36; 9,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,14</t>
+          <t>-1,43; 3,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,72</t>
+          <t>0,44; 5,61</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,6</t>
+          <t>1,96; 6,4</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190,93%</t>
+          <t>186,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>142,25%</t>
+          <t>138,11%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,19</t>
+          <t>-100,0; 122,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-77,16; 270,29</t>
+          <t>-72,94; 272,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 336,84</t>
+          <t>-40,3; 446,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 304,96</t>
+          <t>-13,6; 400,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,56; 414,68</t>
+          <t>18,1; 466,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>52,89; 536,72</t>
+          <t>55,0; 451,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 156,4</t>
+          <t>-37,47; 133,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5,21; 259,11</t>
+          <t>3,17; 247,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>45,64; 339,71</t>
+          <t>36,62; 312,31</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,49</t>
+          <t>-1,83; -0,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,59; -0,28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,06</t>
+          <t>1,26; 3,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,71</t>
+          <t>-1,51; 0,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,83</t>
+          <t>-1,48; 0,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,19</t>
+          <t>4,38; 6,66</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,12</t>
+          <t>-1,45; -0,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,15</t>
+          <t>-1,28; 0,03</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,48</t>
+          <t>3,2; 4,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -22,94</t>
+          <t>-64,94; -27,81</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,54; -14,93</t>
+          <t>-58,43; -12,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36,64; 154,57</t>
+          <t>44,88; 153,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 13,71</t>
+          <t>-23,75; 15,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 16,26</t>
+          <t>-23,44; 16,81</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,96; 117,27</t>
+          <t>65,81; 126,82</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-32,34; -3,4</t>
+          <t>-32,51; -3,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 4,25</t>
+          <t>-29,17; 1,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>54,74; 119,5</t>
+          <t>70,81; 125,34</t>
         </is>
       </c>
     </row>
